--- a/artfynd/A 40555-2024 artfynd.xlsx
+++ b/artfynd/A 40555-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120902686</v>
+        <v>120902811</v>
       </c>
       <c r="B2" t="n">
-        <v>98071</v>
+        <v>79682</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,48 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gammalsjulrissnet, Jmt</t>
@@ -775,7 +762,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Knärot med minst 16 st skott/stjälkar och 1 st fröställning inom ca 0,5 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 40555-2024.</t>
+          <t>Lunglav på flertalet smalvuxna aspar varav riklig påväxt av lunglav längs flera meter på en av asparna. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 40555-2024.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,6 +783,31 @@
       <c r="AI2" t="inlineStr">
         <is>
           <t>Barrskog med gran, tall och inslag av asp och björk på en liten höjd med frisk mark. Olikåldriga träd där många träd har klenare dimensioner. Viss förekomst av död ved. Bottenskikt med tät förekomst av mossor och glest fältskikt med lingon- och blåbärsris.</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Minst 4 st. smalvuxna äldre aspar.</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Grov bark. # Populus tremula # Minst 4 st. smalvuxna äldre aspar.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -813,10 +825,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120915514</v>
+        <v>120910879</v>
       </c>
       <c r="B3" t="n">
-        <v>97977</v>
+        <v>57504</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -825,43 +837,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>504</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -873,13 +881,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503560</v>
+        <v>503675</v>
       </c>
       <c r="R3" t="n">
-        <v>7017886</v>
+        <v>7018047</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -913,7 +921,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Minst 50 st. vissna stjälkar/skott varav 13 st. med fröställningar av guckusko inom ca 8 m2 yta i ett fuktstråk. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 40555-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 40555-2024.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -922,18 +930,17 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Grandominerad luckig skog på frisk-fuktig och fuktig mark som sannolikt har en del kalkhalt. Mestadels träd av klenare dimensioner.</t>
+          <t>Barrskog med tall/gran och inslag av asp och björk. Äldre spår av tidigare brand i form av kolade grova stubbar. I vissa delar finns större block. På frisk mark.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -951,10 +958,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120910879</v>
+        <v>120915514</v>
       </c>
       <c r="B4" t="n">
-        <v>57501</v>
+        <v>97987</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -963,39 +970,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>504</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1007,13 +1018,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503675</v>
+        <v>503560</v>
       </c>
       <c r="R4" t="n">
-        <v>7018047</v>
+        <v>7017886</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1047,7 +1058,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 40555-2024.</t>
+          <t>Minst 50 st. vissna stjälkar/skott varav 13 st. med fröställningar av guckusko inom ca 8 m2 yta i ett fuktstråk. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 40555-2024.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1056,17 +1067,18 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Barrskog med tall/gran och inslag av asp och björk. Äldre spår av tidigare brand i form av kolade grova stubbar. I vissa delar finns större block. På frisk mark.</t>
+          <t>Grandominerad luckig skog på frisk-fuktig och fuktig mark som sannolikt har en del kalkhalt. Mestadels träd av klenare dimensioner.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1084,10 +1096,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120902811</v>
+        <v>120902686</v>
       </c>
       <c r="B5" t="n">
-        <v>79679</v>
+        <v>98081</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1096,35 +1108,48 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gammalsjulrissnet, Jmt</t>
@@ -1171,7 +1196,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Lunglav på flertalet smalvuxna aspar varav riklig påväxt av lunglav längs flera meter på en av asparna. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 40555-2024.</t>
+          <t>Knärot med minst 16 st skott/stjälkar och 1 st fröställning inom ca 0,5 m2 yta. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 40555-2024.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1192,31 +1217,6 @@
       <c r="AI5" t="inlineStr">
         <is>
           <t>Barrskog med gran, tall och inslag av asp och björk på en liten höjd med frisk mark. Olikåldriga träd där många träd har klenare dimensioner. Viss förekomst av död ved. Bottenskikt med tät förekomst av mossor och glest fältskikt med lingon- och blåbärsris.</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>Minst 4 st. smalvuxna äldre aspar.</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Grov bark. # Populus tremula # Minst 4 st. smalvuxna äldre aspar.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1237,7 +1237,7 @@
         <v>120903925</v>
       </c>
       <c r="B6" t="n">
-        <v>79715</v>
+        <v>79718</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1379,10 +1379,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120971718</v>
+        <v>120971460</v>
       </c>
       <c r="B7" t="n">
-        <v>79679</v>
+        <v>79586</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1391,32 +1391,32 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med isidier</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1426,10 +1426,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>503564</v>
+        <v>503556</v>
       </c>
       <c r="R7" t="n">
-        <v>7017959</v>
+        <v>7017943</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Lunglav med gott om yngre småbålar på asp. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 40555-2024.</t>
+          <t>Skinnlav på asp där det även växer lunglav. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 40555-2024.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1524,10 +1524,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120971629</v>
+        <v>120972216</v>
       </c>
       <c r="B8" t="n">
-        <v>79679</v>
+        <v>79682</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>503565</v>
+        <v>503603</v>
       </c>
       <c r="R8" t="n">
-        <v>7017949</v>
+        <v>7017978</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Enstaka bålar av lunglav på asp. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 40555-2024.</t>
+          <t>Lunglav på en knäckt sälg. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 40555-2024.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1626,32 +1626,37 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Barr-/lövbland</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Grandominerad barrskog med inslag av tall, björk och en hel del asp på frisk- och frisk-fuktig mark. Träd med mest liknande dimensioner. Enstaka förekomst av död ved. Fältskikt med lingon- och blåbärsris.</t>
+          <t>Grandominerad barrskog med inslag av tall, björk och asp på frisk- och frisk-fuktig mark. Träd med varierande dimensioner. Enstaka förekomst av död ved. Fältskikt med lingon- och blåbärsris.</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>En knäckt sälg där stor del av stammen fortfarande sitter ihop vid stambrottytan. Trädet är i stort sätt nästan helt dött bortsett från något enstaka levande skott närmare stambasen.</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Bark of dead wood # Salix caprea # En knäckt sälg där stor del av stammen fortfarande sitter ihop vid stambrottytan. Trädet är i stort sätt nästan helt dött bortsett från något enstaka levande skott närmare stambasen.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1669,10 +1674,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120971274</v>
+        <v>120971718</v>
       </c>
       <c r="B9" t="n">
-        <v>79679</v>
+        <v>79682</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1716,10 +1721,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>503556</v>
+        <v>503564</v>
       </c>
       <c r="R9" t="n">
-        <v>7017943</v>
+        <v>7017959</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1756,7 +1761,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Enstaka bålar av lunglav på asp där det även växer skinnlav. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 40555-2024.</t>
+          <t>Lunglav med gott om yngre småbålar på asp. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 40555-2024.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1814,10 +1819,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120972216</v>
+        <v>120971629</v>
       </c>
       <c r="B10" t="n">
-        <v>79679</v>
+        <v>79682</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1861,10 +1866,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>503603</v>
+        <v>503565</v>
       </c>
       <c r="R10" t="n">
-        <v>7017978</v>
+        <v>7017949</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1901,7 +1906,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Lunglav på en knäckt sälg. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 40555-2024.</t>
+          <t>Enstaka bålar av lunglav på asp. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 40555-2024.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1916,37 +1921,32 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barr-/lövbland</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Grandominerad barrskog med inslag av tall, björk och asp på frisk- och frisk-fuktig mark. Träd med varierande dimensioner. Enstaka förekomst av död ved. Fältskikt med lingon- och blåbärsris.</t>
+          <t>Grandominerad barrskog med inslag av tall, björk och en hel del asp på frisk- och frisk-fuktig mark. Träd med mest liknande dimensioner. Enstaka förekomst av död ved. Fältskikt med lingon- och blåbärsris.</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>En knäckt sälg där stor del av stammen fortfarande sitter ihop vid stambrottytan. Trädet är i stort sätt nästan helt dött bortsett från något enstaka levande skott närmare stambasen.</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea # En knäckt sälg där stor del av stammen fortfarande sitter ihop vid stambrottytan. Trädet är i stort sätt nästan helt dött bortsett från något enstaka levande skott närmare stambasen.</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1964,10 +1964,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120971460</v>
+        <v>120971274</v>
       </c>
       <c r="B11" t="n">
-        <v>79583</v>
+        <v>79682</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>med isidier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Skinnlav på asp där det även växer lunglav. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 40555-2024.</t>
+          <t>Enstaka bålar av lunglav på asp där det även växer skinnlav. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 40555-2024.</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 40555-2024 artfynd.xlsx
+++ b/artfynd/A 40555-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120902811</v>
+        <v>120903925</v>
       </c>
       <c r="B2" t="n">
-        <v>79682</v>
+        <v>79718</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,32 +687,32 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -722,13 +722,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>503543</v>
+        <v>503553</v>
       </c>
       <c r="R2" t="n">
-        <v>7017836</v>
+        <v>7017850</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -762,7 +762,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Lunglav på flertalet smalvuxna aspar varav riklig påväxt av lunglav längs flera meter på en av asparna. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 40555-2024.</t>
+          <t>Fina exemplar av luddlav på en asplåga. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 40555-2024.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,19 +795,14 @@
           <t>Populus tremula</t>
         </is>
       </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>Minst 4 st. smalvuxna äldre aspar.</t>
-        </is>
-      </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Populus tremula # Minst 4 st. smalvuxna äldre aspar.</t>
+          <t>Horizontal, dead with ground contact # Populus tremula</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -825,10 +820,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120910879</v>
+        <v>120902811</v>
       </c>
       <c r="B3" t="n">
-        <v>57504</v>
+        <v>79682</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -841,53 +836,44 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gammalsjulrissnet, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503675</v>
+        <v>503543</v>
       </c>
       <c r="R3" t="n">
-        <v>7018047</v>
+        <v>7017836</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -921,7 +907,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 40555-2024.</t>
+          <t>Lunglav på flertalet smalvuxna aspar varav riklig påväxt av lunglav längs flera meter på en av asparna. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 40555-2024.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -930,6 +916,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -940,7 +927,32 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Barrskog med tall/gran och inslag av asp och björk. Äldre spår av tidigare brand i form av kolade grova stubbar. I vissa delar finns större block. På frisk mark.</t>
+          <t>Barrskog med gran, tall och inslag av asp och björk på en liten höjd med frisk mark. Olikåldriga träd där många träd har klenare dimensioner. Viss förekomst av död ved. Bottenskikt med tät förekomst av mossor och glest fältskikt med lingon- och blåbärsris.</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>Minst 4 st. smalvuxna äldre aspar.</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Grov bark. # Populus tremula # Minst 4 st. smalvuxna äldre aspar.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -958,10 +970,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120915514</v>
+        <v>120910879</v>
       </c>
       <c r="B4" t="n">
-        <v>97987</v>
+        <v>57504</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -970,43 +982,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>504</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1018,13 +1026,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503560</v>
+        <v>503675</v>
       </c>
       <c r="R4" t="n">
-        <v>7017886</v>
+        <v>7018047</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1058,7 +1066,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Minst 50 st. vissna stjälkar/skott varav 13 st. med fröställningar av guckusko inom ca 8 m2 yta i ett fuktstråk. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 40555-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 40555-2024.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1067,18 +1075,17 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Grandominerad luckig skog på frisk-fuktig och fuktig mark som sannolikt har en del kalkhalt. Mestadels träd av klenare dimensioner.</t>
+          <t>Barrskog med tall/gran och inslag av asp och björk. Äldre spår av tidigare brand i form av kolade grova stubbar. I vissa delar finns större block. På frisk mark.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1234,10 +1241,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120903925</v>
+        <v>120915514</v>
       </c>
       <c r="B6" t="n">
-        <v>79718</v>
+        <v>97987</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1250,44 +1257,57 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6464</v>
+        <v>504</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gammalsjulrissnet, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503553</v>
+        <v>503560</v>
       </c>
       <c r="R6" t="n">
-        <v>7017850</v>
+        <v>7017886</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1321,7 +1341,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Fina exemplar av luddlav på en asplåga. Obs! fyndplatsen finns inom en avverkningsanmälan med beteckning A 40555-2024.</t>
+          <t>Minst 50 st. vissna stjälkar/skott varav 13 st. med fröställningar av guckusko inom ca 8 m2 yta i ett fuktstråk. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 40555-2024.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1336,32 +1356,12 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Barrskog med gran, tall och inslag av asp och björk på en liten höjd med frisk mark. Olikåldriga träd där många träd har klenare dimensioner. Viss förekomst av död ved. Bottenskikt med tät förekomst av mossor och glest fältskikt med lingon- och blåbärsris.</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Populus tremula</t>
+          <t>Grandominerad luckig skog på frisk-fuktig och fuktig mark som sannolikt har en del kalkhalt. Mestadels träd av klenare dimensioner.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1379,10 +1379,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120971460</v>
+        <v>120971629</v>
       </c>
       <c r="B7" t="n">
-        <v>79586</v>
+        <v>79682</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1391,32 +1391,32 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>med isidier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1426,13 +1426,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>503556</v>
+        <v>503565</v>
       </c>
       <c r="R7" t="n">
-        <v>7017943</v>
+        <v>7017949</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Skinnlav på asp där det även växer lunglav. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 40555-2024.</t>
+          <t>Enstaka bålar av lunglav på asp. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 40555-2024.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1524,7 +1524,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120972216</v>
+        <v>120971274</v>
       </c>
       <c r="B8" t="n">
         <v>79682</v>
@@ -1571,13 +1571,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>503603</v>
+        <v>503556</v>
       </c>
       <c r="R8" t="n">
-        <v>7017978</v>
+        <v>7017943</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Lunglav på en knäckt sälg. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 40555-2024.</t>
+          <t>Enstaka bålar av lunglav på asp där det även växer skinnlav. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 40555-2024.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1626,37 +1626,32 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barr-/lövbland</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Grandominerad barrskog med inslag av tall, björk och asp på frisk- och frisk-fuktig mark. Träd med varierande dimensioner. Enstaka förekomst av död ved. Fältskikt med lingon- och blåbärsris.</t>
+          <t>Grandominerad barrskog med inslag av tall, björk och en hel del asp på frisk- och frisk-fuktig mark. Träd med mest liknande dimensioner. Enstaka förekomst av död ved. Fältskikt med lingon- och blåbärsris.</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>En knäckt sälg där stor del av stammen fortfarande sitter ihop vid stambrottytan. Trädet är i stort sätt nästan helt dött bortsett från något enstaka levande skott närmare stambasen.</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea # En knäckt sälg där stor del av stammen fortfarande sitter ihop vid stambrottytan. Trädet är i stort sätt nästan helt dött bortsett från något enstaka levande skott närmare stambasen.</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1674,10 +1669,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120971718</v>
+        <v>120971460</v>
       </c>
       <c r="B9" t="n">
-        <v>79682</v>
+        <v>79586</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1686,32 +1681,32 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med isidier</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1721,10 +1716,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>503564</v>
+        <v>503556</v>
       </c>
       <c r="R9" t="n">
-        <v>7017959</v>
+        <v>7017943</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1761,7 +1756,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Lunglav med gott om yngre småbålar på asp. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 40555-2024.</t>
+          <t>Skinnlav på asp där det även växer lunglav. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 40555-2024.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1819,7 +1814,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120971629</v>
+        <v>120972216</v>
       </c>
       <c r="B10" t="n">
         <v>79682</v>
@@ -1866,10 +1861,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>503565</v>
+        <v>503603</v>
       </c>
       <c r="R10" t="n">
-        <v>7017949</v>
+        <v>7017978</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1906,7 +1901,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Enstaka bålar av lunglav på asp. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 40555-2024.</t>
+          <t>Lunglav på en knäckt sälg. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 40555-2024.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1921,32 +1916,37 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Barr-/lövbland</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Grandominerad barrskog med inslag av tall, björk och en hel del asp på frisk- och frisk-fuktig mark. Träd med mest liknande dimensioner. Enstaka förekomst av död ved. Fältskikt med lingon- och blåbärsris.</t>
+          <t>Grandominerad barrskog med inslag av tall, björk och asp på frisk- och frisk-fuktig mark. Träd med varierande dimensioner. Enstaka förekomst av död ved. Fältskikt med lingon- och blåbärsris.</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>En knäckt sälg där stor del av stammen fortfarande sitter ihop vid stambrottytan. Trädet är i stort sätt nästan helt dött bortsett från något enstaka levande skott närmare stambasen.</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Bark of dead wood # Salix caprea # En knäckt sälg där stor del av stammen fortfarande sitter ihop vid stambrottytan. Trädet är i stort sätt nästan helt dött bortsett från något enstaka levande skott närmare stambasen.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1964,7 +1964,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120971274</v>
+        <v>120971718</v>
       </c>
       <c r="B11" t="n">
         <v>79682</v>
@@ -2011,10 +2011,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>503556</v>
+        <v>503564</v>
       </c>
       <c r="R11" t="n">
-        <v>7017943</v>
+        <v>7017959</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Enstaka bålar av lunglav på asp där det även växer skinnlav. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 40555-2024.</t>
+          <t>Lunglav med gott om yngre småbålar på asp. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 40555-2024.</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 40555-2024 artfynd.xlsx
+++ b/artfynd/A 40555-2024 artfynd.xlsx
@@ -1379,10 +1379,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120971629</v>
+        <v>120971274</v>
       </c>
       <c r="B7" t="n">
-        <v>79682</v>
+        <v>79685</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1426,13 +1426,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>503565</v>
+        <v>503556</v>
       </c>
       <c r="R7" t="n">
-        <v>7017949</v>
+        <v>7017943</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Enstaka bålar av lunglav på asp. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 40555-2024.</t>
+          <t>Enstaka bålar av lunglav på asp där det även växer skinnlav. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 40555-2024.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1524,10 +1524,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120971274</v>
+        <v>120972216</v>
       </c>
       <c r="B8" t="n">
-        <v>79682</v>
+        <v>79685</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1571,13 +1571,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>503556</v>
+        <v>503603</v>
       </c>
       <c r="R8" t="n">
-        <v>7017943</v>
+        <v>7017978</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Enstaka bålar av lunglav på asp där det även växer skinnlav. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 40555-2024.</t>
+          <t>Lunglav på en knäckt sälg. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 40555-2024.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1626,32 +1626,37 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Barr-/lövbland</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Grandominerad barrskog med inslag av tall, björk och en hel del asp på frisk- och frisk-fuktig mark. Träd med mest liknande dimensioner. Enstaka förekomst av död ved. Fältskikt med lingon- och blåbärsris.</t>
+          <t>Grandominerad barrskog med inslag av tall, björk och asp på frisk- och frisk-fuktig mark. Träd med varierande dimensioner. Enstaka förekomst av död ved. Fältskikt med lingon- och blåbärsris.</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>En knäckt sälg där stor del av stammen fortfarande sitter ihop vid stambrottytan. Trädet är i stort sätt nästan helt dött bortsett från något enstaka levande skott närmare stambasen.</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Bark of dead wood # Salix caprea # En knäckt sälg där stor del av stammen fortfarande sitter ihop vid stambrottytan. Trädet är i stort sätt nästan helt dött bortsett från något enstaka levande skott närmare stambasen.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1669,10 +1674,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120971460</v>
+        <v>120971629</v>
       </c>
       <c r="B9" t="n">
-        <v>79586</v>
+        <v>79685</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1681,32 +1686,32 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>med isidier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1716,13 +1721,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>503556</v>
+        <v>503565</v>
       </c>
       <c r="R9" t="n">
-        <v>7017943</v>
+        <v>7017949</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1756,7 +1761,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Skinnlav på asp där det även växer lunglav. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 40555-2024.</t>
+          <t>Enstaka bålar av lunglav på asp. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 40555-2024.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1814,10 +1819,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120972216</v>
+        <v>120971460</v>
       </c>
       <c r="B10" t="n">
-        <v>79682</v>
+        <v>79589</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1826,32 +1831,32 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med isidier</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1861,13 +1866,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>503603</v>
+        <v>503556</v>
       </c>
       <c r="R10" t="n">
-        <v>7017978</v>
+        <v>7017943</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1901,7 +1906,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Lunglav på en knäckt sälg. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 40555-2024.</t>
+          <t>Skinnlav på asp där det även växer lunglav. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 40555-2024.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1916,37 +1921,32 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barr-/lövbland</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Grandominerad barrskog med inslag av tall, björk och asp på frisk- och frisk-fuktig mark. Träd med varierande dimensioner. Enstaka förekomst av död ved. Fältskikt med lingon- och blåbärsris.</t>
+          <t>Grandominerad barrskog med inslag av tall, björk och en hel del asp på frisk- och frisk-fuktig mark. Träd med mest liknande dimensioner. Enstaka förekomst av död ved. Fältskikt med lingon- och blåbärsris.</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>En knäckt sälg där stor del av stammen fortfarande sitter ihop vid stambrottytan. Trädet är i stort sätt nästan helt dött bortsett från något enstaka levande skott närmare stambasen.</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea # En knäckt sälg där stor del av stammen fortfarande sitter ihop vid stambrottytan. Trädet är i stort sätt nästan helt dött bortsett från något enstaka levande skott närmare stambasen.</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1967,7 +1967,7 @@
         <v>120971718</v>
       </c>
       <c r="B11" t="n">
-        <v>79682</v>
+        <v>79685</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 40555-2024 artfynd.xlsx
+++ b/artfynd/A 40555-2024 artfynd.xlsx
@@ -973,7 +973,7 @@
         <v>120910879</v>
       </c>
       <c r="B4" t="n">
-        <v>57504</v>
+        <v>57643</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">

--- a/artfynd/A 40555-2024 artfynd.xlsx
+++ b/artfynd/A 40555-2024 artfynd.xlsx
@@ -973,7 +973,7 @@
         <v>120910879</v>
       </c>
       <c r="B4" t="n">
-        <v>57643</v>
+        <v>57644</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
